--- a/Heuristic/data/test/production_capacity_scenarios.xlsx
+++ b/Heuristic/data/test/production_capacity_scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Heuristic/data/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E6874F5-C5E8-436D-A2D6-3BF5C1616433}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2986C41C-5A14-4C86-BB0D-709106DA56A0}"/>
   <bookViews>
-    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -178,10 +178,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -879,7 +875,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
